--- a/Result/profitability/3622.xlsx
+++ b/Result/profitability/3622.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.6</v>
       </c>
       <c r="M2" t="n">
-        <v>1.5675</v>
+        <v>1.315</v>
       </c>
       <c r="N2" t="n">
-        <v>42.195</v>
+        <v>41.595</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>2.23</v>
       </c>
       <c r="M3" t="n">
-        <v>1.5925</v>
+        <v>1.5025</v>
       </c>
       <c r="N3" t="n">
-        <v>39.9975</v>
+        <v>39.11375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>3.12</v>
       </c>
       <c r="M4" t="n">
-        <v>1.89125</v>
+        <v>1.725</v>
       </c>
       <c r="N4" t="n">
-        <v>38.0675</v>
+        <v>36.92124999999999</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>3.6</v>
       </c>
       <c r="M5" t="n">
-        <v>2.17375</v>
+        <v>2.08125</v>
       </c>
       <c r="N5" t="n">
-        <v>35.485</v>
+        <v>34.305</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1137,10 +1137,10 @@
         <v>4.3</v>
       </c>
       <c r="M6" t="n">
-        <v>2.6175</v>
+        <v>2.26875</v>
       </c>
       <c r="N6" t="n">
-        <v>33.9175</v>
+        <v>32.8225</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>5.86</v>
       </c>
       <c r="M7" t="n">
-        <v>3</v>
+        <v>2.85125</v>
       </c>
       <c r="N7" t="n">
-        <v>33.06125</v>
+        <v>32.7325</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1279,13 +1279,13 @@
         <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>7.37</v>
       </c>
       <c r="M8" t="n">
-        <v>3.77125</v>
+        <v>3.63625</v>
       </c>
       <c r="N8" t="n">
-        <v>32.91875</v>
+        <v>32.72875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>2.45</v>
       </c>
       <c r="M13" t="n">
-        <v>5.476249999999999</v>
+        <v>5.47625</v>
       </c>
       <c r="N13" t="n">
         <v>31.98625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3622</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>422</v>
+      </c>
+      <c r="D75" t="n">
+        <v>266</v>
+      </c>
+      <c r="E75" t="n">
+        <v>156</v>
+      </c>
+      <c r="F75" t="n">
+        <v>36.91</v>
+      </c>
+      <c r="G75" t="n">
+        <v>93</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>22.15%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-53</v>
+      </c>
+      <c r="J75" t="n">
+        <v>41</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.24375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>42.33375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.9908256880733946</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.520000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03955243299505606</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.9866666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-9.440000000000005</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.2036677454153183</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
